--- a/vignettes/demo_data_pos/variable_info.xlsx
+++ b/vignettes/demo_data_pos/variable_info.xlsx
@@ -8062,7 +8062,7 @@
         <v>262</v>
       </c>
       <c r="B261" t="n">
-        <v>232.114853974259</v>
+        <v>232.11485397426</v>
       </c>
       <c r="C261" t="n">
         <v>106.927337646484</v>
@@ -10086,7 +10086,7 @@
         <v>446</v>
       </c>
       <c r="B445" t="n">
-        <v>293.570619187041</v>
+        <v>293.57061918704</v>
       </c>
       <c r="C445" t="n">
         <v>229.343482971191</v>
@@ -17522,7 +17522,7 @@
         <v>1122</v>
       </c>
       <c r="B1121" t="n">
-        <v>532.296147610759</v>
+        <v>532.29614761076</v>
       </c>
       <c r="C1121" t="n">
         <v>51.8119277954102</v>
@@ -18589,7 +18589,7 @@
         <v>1219</v>
       </c>
       <c r="B1218" t="n">
-        <v>578.416170388509</v>
+        <v>578.41617038851</v>
       </c>
       <c r="C1218" t="n">
         <v>453.617553710938</v>
@@ -19766,7 +19766,7 @@
         <v>1326</v>
       </c>
       <c r="B1325" t="n">
-        <v>691.187874615759</v>
+        <v>691.18787461576</v>
       </c>
       <c r="C1325" t="n">
         <v>227.818183898926</v>
@@ -20492,7 +20492,7 @@
         <v>1392</v>
       </c>
       <c r="B1391" t="n">
-        <v>746.597824654701</v>
+        <v>746.5978246547</v>
       </c>
       <c r="C1391" t="n">
         <v>628.800903320312</v>
@@ -20932,7 +20932,7 @@
         <v>1432</v>
       </c>
       <c r="B1431" t="n">
-        <v>783.569446754791</v>
+        <v>783.56944675479</v>
       </c>
       <c r="C1431" t="n">
         <v>628.158325195312</v>
@@ -22791,7 +22791,7 @@
         <v>1601</v>
       </c>
       <c r="B1600" t="n">
-        <v>1145.40586641399</v>
+        <v>1145.405866414</v>
       </c>
       <c r="C1600" t="n">
         <v>179.795257568359</v>
